--- a/production data.xlsx
+++ b/production data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tushar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2771EACF-159C-44E8-B2F2-26A7F989F54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C345CF92-0AC3-4A6B-8C0F-AB2C6F324AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{609407B5-4368-44A2-9970-18649C95028E}"/>
   </bookViews>
